--- a/teacher_feedback_forms/019_teacher_feedback_form--teacher_feedback_forms.xlsx
+++ b/teacher_feedback_forms/019_teacher_feedback_form--teacher_feedback_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>How was teacher performance?</t>
+          <t>How was the teacher's performance?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lesson_planning</t>
+          <t>lesson_planning_and_delivery</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lesson planning and delivery</t>
+          <t>How was lesson planning and delivery?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>teaching_styles</t>
+          <t>teaching_styles_and_techniques</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Teaching styles and techniques</t>
+          <t>What are your thoughts on the teacher's teaching styles and techniques?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Student engagement</t>
+          <t>How engaged do you feel with the teacher?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -597,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Teacher availability</t>
+          <t>What is your feedback frequency on the teacher's availability?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Feedback frequency</t>
+          <t>How often do you receive feedback from the teacher?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Teacher support</t>
+          <t>How does the teacher support you in your learning?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Helpfulness</t>
+          <t>How helpful do you find the teacher's responses to your questions?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Professionalism</t>
+          <t>Does the teacher demonstrate professional behavior?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -712,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -722,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Effectiveness</t>
+          <t>How effective is the teacher in their role?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -735,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -745,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>How does the teacher communicate effectively with you?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Friendly</t>
+          <t>How friendly and approachable is the teacher?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>How responsive is the teacher to your needs?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -804,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -814,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Supportive</t>
+          <t>Does the teacher provide supportive guidance and feedback?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Responsible</t>
+          <t>Does the teacher take responsibility for their actions and decisions?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -850,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -860,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prepared</t>
+          <t>How prepared is the teacher for classes and lessons?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -873,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>teacher_professionals</t>
+          <t>teacher_professionalism_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Professionals</t>
+          <t>How professional is the teacher in their interactions with you?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,315 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>teacher_punctuality</t>
+          <t>punctuality</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Punctuality</t>
+          <t>Does the teacher exhibit punctuality in their work?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>teacher_punctuality</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Punctuality</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1221,6 +932,348 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>teacher_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>highly_effective</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Highly Effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>teacher_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>moderately_effective</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Moderately Effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>teacher_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>not_very_effective</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Not Very Effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>teacher_communication_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>clearly</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>teacher_communication_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>effectively</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Effectively</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>teacher_communication_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>not_clearly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Not Clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>teacher_communication_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>not_effectively</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Not Effectively</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>teacher_supportive_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>teacher_supportive_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>teacher_supportive_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>teacher_supportive_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>teacher_prepared_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>very_prepared</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Very Prepared</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>teacher_prepared_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>somewhat_prepared</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Somewhat Prepared</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>teacher_prepared_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>not_very_prepared</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not Very Prepared</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>teacher_professionalism_2_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>very_professional</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Very Professional</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>teacher_professionalism_2_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>somewhat_professional</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Somewhat Professional</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>teacher_professionalism_2_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>not_very_professional</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Not Very Professional</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>teacher_professionalism_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>not_at_all_professional</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Not at All Professional</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
